--- a/Windows_Ransomware_Intrusion/evidence/PrefetchFiles/NANO.EXE-D138E751.xlsx
+++ b/Windows_Ransomware_Intrusion/evidence/PrefetchFiles/NANO.EXE-D138E751.xlsx
@@ -1,25 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Emma\Desktop\Parsed\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emma/DFIR-Simulation-Platform/Windows_Ransomware_Intrusion/evidence/PrefetchFiles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5FF1587-25DC-4D75-BF5E-9F2A8789416A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41DFBDF1-22AF-4D48-ADF9-F8702C5BBAEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6984" yWindow="672" windowWidth="15024" windowHeight="11064" xr2:uid="{56943142-AB8E-4206-800C-19C10C7675D7}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="22000" windowHeight="11780" xr2:uid="{56943142-AB8E-4206-800C-19C10C7675D7}"/>
   </bookViews>
   <sheets>
     <sheet name="NANO.EXE-D138E751" sheetId="2" r:id="rId1"/>
     <sheet name="NANO.EXE-D138E751_Timeline" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="ExternalData_1" localSheetId="0" hidden="1">'NANO.EXE-D138E751'!$A$1:$AA$2</definedName>
-    <definedName name="ExternalData_1" localSheetId="1" hidden="1">'NANO.EXE-D138E751_Timeline'!$A$1:$B$7</definedName>
-    <definedName name="ExternalData_1" localSheetId="1" hidden="1">'NANO.EXE-D138E751_Timeline'!$A$1:$B$7</definedName>
+    <definedName name="ExternalData_1" localSheetId="0" hidden="1">'NANO.EXE-D138E751'!$A$1:$V$2</definedName>
+    <definedName name="ExternalData_1" localSheetId="1" hidden="1">'NANO.EXE-D138E751_Timeline'!$A$1:$B$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -56,22 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="38">
-  <si>
-    <t>Note</t>
-  </si>
-  <si>
-    <t>SourceFilename</t>
-  </si>
-  <si>
-    <t>SourceCreated</t>
-  </si>
-  <si>
-    <t>SourceModified</t>
-  </si>
-  <si>
-    <t>SourceAccessed</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="32">
   <si>
     <t>ExecutableName</t>
   </si>
@@ -140,9 +124,6 @@
   </si>
   <si>
     <t/>
-  </si>
-  <si>
-    <t>C:\Users\Emma\Desktop\evidence\System\NANO.EXE-D138E751.pf</t>
   </si>
   <si>
     <t>NANO.EXE</t>
@@ -212,78 +193,63 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="26">
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="m/d/yyyy\ h:mm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="m/d/yyyy\ h:mm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="m/d/yyyy\ h:mm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="m/d/yyyy\ h:mm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="m/d/yyyy\ h:mm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="m/d/yyyy\ h:mm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="m/d/yyyy\ h:mm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="m/d/yyyy\ h:mm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="m/d/yyyy\ h:mm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="m/d/yyyy\ h:mm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="m/d/yyyy\ h:mm"/>
+  <dxfs count="21">
+    <dxf>
+      <numFmt numFmtId="27" formatCode="m/d/yy\ h:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="27" formatCode="m/d/yy\ h:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="m/d/yyyy\ h:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="m/d/yyyy\ h:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="m/d/yyyy\ h:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="m/d/yyyy\ h:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="m/d/yyyy\ h:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="m/d/yyyy\ h:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -307,12 +273,7 @@
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_1" connectionId="1" xr16:uid="{9C83D082-DCB3-4D62-A8C0-042B133A2CD4}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
   <queryTableRefresh nextId="28">
-    <queryTableFields count="27">
-      <queryTableField id="1" name="Note" tableColumnId="1"/>
-      <queryTableField id="2" name="SourceFilename" tableColumnId="2"/>
-      <queryTableField id="3" name="SourceCreated" tableColumnId="3"/>
-      <queryTableField id="4" name="SourceModified" tableColumnId="4"/>
-      <queryTableField id="5" name="SourceAccessed" tableColumnId="5"/>
+    <queryTableFields count="22">
       <queryTableField id="6" name="ExecutableName" tableColumnId="6"/>
       <queryTableField id="7" name="Hash" tableColumnId="7"/>
       <queryTableField id="8" name="Size" tableColumnId="8"/>
@@ -336,6 +297,13 @@
       <queryTableField id="26" name="FilesLoaded" tableColumnId="26"/>
       <queryTableField id="27" name="ParsingError" tableColumnId="27"/>
     </queryTableFields>
+    <queryTableDeletedFields count="5">
+      <deletedField name="Note"/>
+      <deletedField name="SourceFilename"/>
+      <deletedField name="SourceCreated"/>
+      <deletedField name="SourceModified"/>
+      <deletedField name="SourceAccessed"/>
+    </queryTableDeletedFields>
   </queryTableRefresh>
 </queryTable>
 </file>
@@ -352,35 +320,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{36B09256-FEB1-48D2-8D0D-CA311D0D1B50}" name="_20260429011530_PECmd_Output" displayName="_20260429011530_PECmd_Output" ref="A1:AA2" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:AA2" xr:uid="{36B09256-FEB1-48D2-8D0D-CA311D0D1B50}"/>
-  <tableColumns count="27">
-    <tableColumn id="1" xr3:uid="{2219BE38-5195-44D4-89F7-6DCDD0B7E424}" uniqueName="1" name="Note" queryTableFieldId="1" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{4BD9288B-C8A7-4D54-BBFA-B5C40B4607BA}" uniqueName="2" name="SourceFilename" queryTableFieldId="2" dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{BA6E4065-F67A-44FE-98AD-946DD85C1C62}" uniqueName="3" name="SourceCreated" queryTableFieldId="3" dataDxfId="23"/>
-    <tableColumn id="4" xr3:uid="{DBF864D8-C1F6-4145-BA48-4CF635A609CC}" uniqueName="4" name="SourceModified" queryTableFieldId="4" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{7AB57028-FB98-46FE-9149-0937356E0F0A}" uniqueName="5" name="SourceAccessed" queryTableFieldId="5" dataDxfId="21"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{36B09256-FEB1-48D2-8D0D-CA311D0D1B50}" name="_20260429011530_PECmd_Output" displayName="_20260429011530_PECmd_Output" ref="A1:V2" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:V2" xr:uid="{36B09256-FEB1-48D2-8D0D-CA311D0D1B50}"/>
+  <tableColumns count="22">
     <tableColumn id="6" xr3:uid="{B77B1119-5832-4D51-A75C-93B131DF606B}" uniqueName="6" name="ExecutableName" queryTableFieldId="6" dataDxfId="20"/>
     <tableColumn id="7" xr3:uid="{1DF1045D-3F3C-4385-BE6A-14C8AD79505A}" uniqueName="7" name="Hash" queryTableFieldId="7" dataDxfId="19"/>
     <tableColumn id="8" xr3:uid="{018381C5-BE18-49E8-AC15-1AD7D373C09B}" uniqueName="8" name="Size" queryTableFieldId="8"/>
     <tableColumn id="9" xr3:uid="{4525FCD7-3644-4530-9E80-3EED2AE69352}" uniqueName="9" name="Version" queryTableFieldId="9" dataDxfId="18"/>
     <tableColumn id="10" xr3:uid="{862A74C2-58AB-4E77-8A5A-BFB6312EBFB1}" uniqueName="10" name="RunCount" queryTableFieldId="10"/>
-    <tableColumn id="11" xr3:uid="{75983971-468C-4BDA-85BD-1537A86FD27D}" uniqueName="11" name="LastRun" queryTableFieldId="11" dataDxfId="17"/>
-    <tableColumn id="12" xr3:uid="{3DD751CB-6DE4-42B6-9C23-B73C0ED8543C}" uniqueName="12" name="PreviousRun0" queryTableFieldId="12" dataDxfId="16"/>
-    <tableColumn id="13" xr3:uid="{CE44199F-CF6C-4CB3-9F54-253870F2A953}" uniqueName="13" name="PreviousRun1" queryTableFieldId="13" dataDxfId="15"/>
-    <tableColumn id="14" xr3:uid="{F3E9B972-A852-4E15-A18C-5008A40FCDC9}" uniqueName="14" name="PreviousRun2" queryTableFieldId="14" dataDxfId="14"/>
-    <tableColumn id="15" xr3:uid="{29CD4F66-A1BC-44E7-895D-F476D00303EB}" uniqueName="15" name="PreviousRun3" queryTableFieldId="15" dataDxfId="13"/>
-    <tableColumn id="16" xr3:uid="{5193F0E9-2F08-4CDA-975A-918748494B03}" uniqueName="16" name="PreviousRun4" queryTableFieldId="16" dataDxfId="12"/>
-    <tableColumn id="17" xr3:uid="{A90010C2-0113-498A-A2D2-CA3F70F4B6E5}" uniqueName="17" name="PreviousRun5" queryTableFieldId="17" dataDxfId="11"/>
-    <tableColumn id="18" xr3:uid="{8B38FC31-3566-4E1C-BD44-ED2399DC0FD0}" uniqueName="18" name="PreviousRun6" queryTableFieldId="18" dataDxfId="10"/>
-    <tableColumn id="19" xr3:uid="{47E3947E-5406-4A9D-AE67-0541247C429A}" uniqueName="19" name="Volume0Name" queryTableFieldId="19" dataDxfId="9"/>
-    <tableColumn id="20" xr3:uid="{4F9138D9-4FE8-48E4-83B1-701E801DDC0A}" uniqueName="20" name="Volume0Serial" queryTableFieldId="20" dataDxfId="8"/>
-    <tableColumn id="21" xr3:uid="{52B2890B-2BD2-40A7-82F5-2EFDFC3D6913}" uniqueName="21" name="Volume0Created" queryTableFieldId="21" dataDxfId="7"/>
-    <tableColumn id="22" xr3:uid="{81FE6981-EBC2-4C3F-AA1F-20366B6906EF}" uniqueName="22" name="Volume1Name" queryTableFieldId="22" dataDxfId="6"/>
-    <tableColumn id="23" xr3:uid="{1E1C941E-089A-4D98-8FDD-52A8342841B0}" uniqueName="23" name="Volume1Serial" queryTableFieldId="23" dataDxfId="5"/>
-    <tableColumn id="24" xr3:uid="{E7D68EAC-40DE-4FD3-A169-9727647222EC}" uniqueName="24" name="Volume1Created" queryTableFieldId="24" dataDxfId="4"/>
-    <tableColumn id="25" xr3:uid="{5A1E267D-770C-40ED-B088-CD6CB894F3EE}" uniqueName="25" name="Directories" queryTableFieldId="25" dataDxfId="3"/>
-    <tableColumn id="26" xr3:uid="{64086EB8-C0D2-47E8-9876-DCECFFA6AC7B}" uniqueName="26" name="FilesLoaded" queryTableFieldId="26" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{75983971-468C-4BDA-85BD-1537A86FD27D}" uniqueName="11" name="LastRun" queryTableFieldId="11" dataDxfId="1"/>
+    <tableColumn id="12" xr3:uid="{3DD751CB-6DE4-42B6-9C23-B73C0ED8543C}" uniqueName="12" name="PreviousRun0" queryTableFieldId="12" dataDxfId="0"/>
+    <tableColumn id="13" xr3:uid="{CE44199F-CF6C-4CB3-9F54-253870F2A953}" uniqueName="13" name="PreviousRun1" queryTableFieldId="13" dataDxfId="17"/>
+    <tableColumn id="14" xr3:uid="{F3E9B972-A852-4E15-A18C-5008A40FCDC9}" uniqueName="14" name="PreviousRun2" queryTableFieldId="14" dataDxfId="16"/>
+    <tableColumn id="15" xr3:uid="{29CD4F66-A1BC-44E7-895D-F476D00303EB}" uniqueName="15" name="PreviousRun3" queryTableFieldId="15" dataDxfId="15"/>
+    <tableColumn id="16" xr3:uid="{5193F0E9-2F08-4CDA-975A-918748494B03}" uniqueName="16" name="PreviousRun4" queryTableFieldId="16" dataDxfId="14"/>
+    <tableColumn id="17" xr3:uid="{A90010C2-0113-498A-A2D2-CA3F70F4B6E5}" uniqueName="17" name="PreviousRun5" queryTableFieldId="17" dataDxfId="13"/>
+    <tableColumn id="18" xr3:uid="{8B38FC31-3566-4E1C-BD44-ED2399DC0FD0}" uniqueName="18" name="PreviousRun6" queryTableFieldId="18" dataDxfId="12"/>
+    <tableColumn id="19" xr3:uid="{47E3947E-5406-4A9D-AE67-0541247C429A}" uniqueName="19" name="Volume0Name" queryTableFieldId="19" dataDxfId="11"/>
+    <tableColumn id="20" xr3:uid="{4F9138D9-4FE8-48E4-83B1-701E801DDC0A}" uniqueName="20" name="Volume0Serial" queryTableFieldId="20" dataDxfId="10"/>
+    <tableColumn id="21" xr3:uid="{52B2890B-2BD2-40A7-82F5-2EFDFC3D6913}" uniqueName="21" name="Volume0Created" queryTableFieldId="21" dataDxfId="9"/>
+    <tableColumn id="22" xr3:uid="{81FE6981-EBC2-4C3F-AA1F-20366B6906EF}" uniqueName="22" name="Volume1Name" queryTableFieldId="22" dataDxfId="8"/>
+    <tableColumn id="23" xr3:uid="{1E1C941E-089A-4D98-8FDD-52A8342841B0}" uniqueName="23" name="Volume1Serial" queryTableFieldId="23" dataDxfId="7"/>
+    <tableColumn id="24" xr3:uid="{E7D68EAC-40DE-4FD3-A169-9727647222EC}" uniqueName="24" name="Volume1Created" queryTableFieldId="24" dataDxfId="6"/>
+    <tableColumn id="25" xr3:uid="{5A1E267D-770C-40ED-B088-CD6CB894F3EE}" uniqueName="25" name="Directories" queryTableFieldId="25" dataDxfId="5"/>
+    <tableColumn id="26" xr3:uid="{64086EB8-C0D2-47E8-9876-DCECFFA6AC7B}" uniqueName="26" name="FilesLoaded" queryTableFieldId="26" dataDxfId="4"/>
     <tableColumn id="27" xr3:uid="{814B2B1B-F27D-4C7E-9F11-E107763D96CA}" uniqueName="27" name="ParsingError" queryTableFieldId="27"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -388,11 +351,11 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{22200995-46A1-4940-B178-F08BEF52ACD1}" name="_20260429011530_PECmd_Output_Timeline" displayName="_20260429011530_PECmd_Output_Timeline" ref="A1:B7" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:B7" xr:uid="{43798B1D-5D24-46E1-8676-FC539907AB74}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{22200995-46A1-4940-B178-F08BEF52ACD1}" name="_20260429011530_PECmd_Output_Timeline" displayName="_20260429011530_PECmd_Output_Timeline" ref="A1:B3" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:B3" xr:uid="{43798B1D-5D24-46E1-8676-FC539907AB74}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{25279398-AC1A-47A0-A6D1-5BEE9629EF66}" uniqueName="1" name="RunTime" queryTableFieldId="1" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{EEE0DE85-3FD6-440B-8D5A-ACD78B381683}" uniqueName="2" name="ExecutableName" queryTableFieldId="2" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{25279398-AC1A-47A0-A6D1-5BEE9629EF66}" uniqueName="1" name="RunTime" queryTableFieldId="1" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{EEE0DE85-3FD6-440B-8D5A-ACD78B381683}" uniqueName="2" name="ExecutableName" queryTableFieldId="2" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -715,32 +678,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C96AC1A-6140-47BE-875E-02768AFD1F6E}">
-  <dimension ref="A1:AA2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:V2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="57" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.21875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.77734375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="18" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="34.6640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="255.77734375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="13" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="34.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="255.83203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -807,102 +765,64 @@
       <c r="V1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2">
+        <v>16638</v>
+      </c>
+      <c r="D2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2" s="1">
+        <v>46136.773356481484</v>
+      </c>
+      <c r="G2" s="1">
+        <v>46136.770567129628</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" t="s">
         <v>22</v>
       </c>
-      <c r="X1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA1" t="s">
+      <c r="M2" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="O2" t="s">
         <v>27</v>
       </c>
-      <c r="B2" t="s">
+      <c r="P2" s="1">
+        <v>46133.084305555552</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>22</v>
+      </c>
+      <c r="R2" t="s">
+        <v>22</v>
+      </c>
+      <c r="S2" t="s">
+        <v>22</v>
+      </c>
+      <c r="T2" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="1">
-        <v>46140.404652777775</v>
-      </c>
-      <c r="D2" s="1">
-        <v>46140.552534722221</v>
-      </c>
-      <c r="E2" s="1">
-        <v>46141.052430555559</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="U2" t="s">
         <v>29</v>
       </c>
-      <c r="G2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H2">
-        <v>16638</v>
-      </c>
-      <c r="I2" t="s">
-        <v>31</v>
-      </c>
-      <c r="J2">
-        <v>6</v>
-      </c>
-      <c r="K2" s="1">
-        <v>46136.949675925927</v>
-      </c>
-      <c r="L2" s="1">
-        <v>46136.94872685185</v>
-      </c>
-      <c r="M2" s="1">
-        <v>46136.945277777777</v>
-      </c>
-      <c r="N2" s="1">
-        <v>46136.944479166668</v>
-      </c>
-      <c r="O2" s="1">
-        <v>46136.773356481484</v>
-      </c>
-      <c r="P2" s="1">
-        <v>46136.770567129628</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>27</v>
-      </c>
-      <c r="R2" t="s">
-        <v>27</v>
-      </c>
-      <c r="S2" t="s">
-        <v>32</v>
-      </c>
-      <c r="T2" t="s">
-        <v>33</v>
-      </c>
-      <c r="U2" s="1">
-        <v>46133.084305555552</v>
-      </c>
-      <c r="V2" t="s">
-        <v>27</v>
-      </c>
-      <c r="W2" t="s">
-        <v>27</v>
-      </c>
-      <c r="X2" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>34</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AA2" t="b">
+      <c r="V2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -916,67 +836,35 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CE129FA-0E79-446F-8161-550EE961B606}">
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="153.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
-        <v>46136.949675925927</v>
+        <v>46136.773356481484</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
-        <v>46136.94872685185</v>
+        <v>46136.770567129628</v>
       </c>
       <c r="B3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
-        <v>46136.945277777777</v>
-      </c>
-      <c r="B4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
-        <v>46136.944479166668</v>
-      </c>
-      <c r="B5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
-        <v>46136.773356481484</v>
-      </c>
-      <c r="B6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="1">
-        <v>46136.770567129628</v>
-      </c>
-      <c r="B7" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
